--- a/Fischer_Tropsch/FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_H2_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF8A9F5-9320-4F1C-AE89-6154C5953E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9D341D-92D8-4EB3-A1D1-BA2B8370CD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1426,10 +1426,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1589,122 +1589,100 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1712,11 +1690,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2057,46 +2035,46 @@
   <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="14"/>
+    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="24" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2113,338 +2091,338 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="57"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="2">
         <v>50</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="57"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="16">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="14">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="57"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="44"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="3">
         <v>0.03</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="57"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="44"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="4">
         <v>20</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="57"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="44"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="3">
         <v>0.08</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="57"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="44"/>
+      <c r="B8" s="54" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <v>38.99</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="57"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="2">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="57"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="2">
         <v>2440</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="2" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="57"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="3">
         <v>0.03</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="2">
         <v>0.63</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="1" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="57"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="2">
         <v>4.8600000000000003</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="14" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="2">
         <v>0.39</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="57"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="4">
         <v>20</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="21" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="18">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
-      <c r="B17" s="68" t="s">
+      <c r="A17" s="44"/>
+      <c r="B17" s="54" t="s">
         <v>238</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="19">
         <v>3.7</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="57"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="14" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="3">
         <v>0.27</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="57"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="3">
         <v>700</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="57"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="14" t="s">
+      <c r="A20" s="44"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="3">
         <v>0.02</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="44"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="3">
         <v>20</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="21" t="s">
+      <c r="A22" s="44"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="18">
         <v>0.05</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="57"/>
-      <c r="B23" s="55" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="42" t="s">
         <v>386</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="35" t="s">
         <v>387</v>
       </c>
       <c r="E23" s="11">
@@ -2455,12 +2433,12 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
-      <c r="B24" s="55"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="42"/>
       <c r="C24" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="35" t="s">
         <v>388</v>
       </c>
       <c r="E24" s="11">
@@ -2471,12 +2449,12 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="57"/>
-      <c r="B25" s="55"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="35" t="s">
         <v>389</v>
       </c>
       <c r="E25" s="11">
@@ -2487,12 +2465,12 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="57"/>
-      <c r="B26" s="55"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="42"/>
       <c r="C26" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="35" t="s">
         <v>391</v>
       </c>
       <c r="E26" s="10">
@@ -2503,24 +2481,24 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="57"/>
-      <c r="B27" s="55"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="35" t="s">
         <v>392</v>
       </c>
       <c r="E27" s="10">
         <v>2.5</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="35" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="57"/>
-      <c r="B28" s="55"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="1" t="s">
         <v>394</v>
       </c>
@@ -2535,8 +2513,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="57"/>
-      <c r="B29" s="55"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
         <v>397</v>
       </c>
@@ -2551,12 +2529,12 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="57"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="42"/>
       <c r="C30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="35" t="s">
         <v>400</v>
       </c>
       <c r="E30" s="9">
@@ -2567,12 +2545,12 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="57"/>
-      <c r="B31" s="55"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="35" t="s">
         <v>401</v>
       </c>
       <c r="E31" s="10">
@@ -2583,10 +2561,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="46" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -2595,7 +2573,7 @@
       <c r="D32" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="25">
         <v>490</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -2603,120 +2581,120 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="57"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="44"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="3">
         <v>0.01</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="44"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="4">
         <v>20</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="57"/>
-      <c r="B35" s="61"/>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="44"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="26">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="57"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="44"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="3">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="57"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="44"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="3">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="57"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="44"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="3">
         <v>0.05</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="57"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="44"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="18">
         <v>0</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="57"/>
-      <c r="B40" s="63" t="s">
+      <c r="A40" s="44"/>
+      <c r="B40" s="49" t="s">
         <v>278</v>
       </c>
       <c r="C40" s="12" t="s">
@@ -2725,7 +2703,7 @@
       <c r="D40" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="25">
         <v>2.83</v>
       </c>
       <c r="F40" s="12" t="s">
@@ -2733,654 +2711,654 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="57"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="44"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="3">
         <v>0.03</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="57"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="44"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="4">
         <v>30</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="57"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="44"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="3">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="57"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="44"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="3">
         <v>0.98</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="57"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="14" t="s">
+      <c r="A45" s="44"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="3">
         <v>0.98</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="14" t="s">
+      <c r="A46" s="44"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="3">
         <v>0.05</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="57"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="21" t="s">
+      <c r="A47" s="44"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="18">
         <v>0</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="57"/>
-      <c r="B48" s="63" t="s">
+      <c r="A48" s="44"/>
+      <c r="B48" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="19">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="57"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="44"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="2">
         <f>E50*4</f>
         <v>424</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="57"/>
-      <c r="B50" s="65"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="44"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="2">
         <v>106</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="57"/>
-      <c r="B51" s="65"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="44"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="57"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="44"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="3">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="57"/>
-      <c r="B53" s="65"/>
-      <c r="C53" s="14" t="s">
+      <c r="A53" s="44"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="3">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="65"/>
-      <c r="C54" s="14" t="s">
+      <c r="A54" s="44"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="2">
         <v>0.25</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="57"/>
-      <c r="B55" s="65"/>
-      <c r="C55" s="14" t="s">
+      <c r="A55" s="44"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="3">
         <v>0</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="57"/>
-      <c r="B56" s="65"/>
-      <c r="C56" s="14" t="s">
+      <c r="A56" s="44"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="4">
         <v>15</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="58"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="31" t="s">
+      <c r="A57" s="45"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="28">
         <v>0.1</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="44" t="s">
+      <c r="B58" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="C58" s="35" t="s">
+      <c r="C58" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="E58" s="36">
+      <c r="E58" s="32">
         <v>0.1699</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="31" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="59"/>
-      <c r="B59" s="46" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="44"/>
+      <c r="B59" s="39" t="s">
         <v>405</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="D59" s="47" t="s">
+      <c r="D59" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="41">
         <v>5</v>
       </c>
-      <c r="F59" s="47" t="s">
+      <c r="F59" s="40" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="59"/>
-      <c r="B60" s="43" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="44"/>
+      <c r="B60" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="C60" s="42" t="s">
+      <c r="C60" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="D60" s="42" t="s">
+      <c r="D60" s="35" t="s">
         <v>403</v>
       </c>
       <c r="E60" s="10">
         <v>0</v>
       </c>
-      <c r="F60" s="42" t="s">
+      <c r="F60" s="35" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="57"/>
-      <c r="B61" s="63" t="s">
+      <c r="A61" s="44"/>
+      <c r="B61" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="19">
         <v>0.99</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="F61" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="57"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="14" t="s">
+      <c r="A62" s="44"/>
+      <c r="B62" s="47"/>
+      <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E62" s="5">
         <v>1100</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="57"/>
-      <c r="B63" s="61"/>
-      <c r="C63" s="14" t="s">
+      <c r="A63" s="44"/>
+      <c r="B63" s="47"/>
+      <c r="C63" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="5">
         <v>17.84</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="57"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="14" t="s">
+      <c r="A64" s="44"/>
+      <c r="B64" s="47"/>
+      <c r="C64" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E64" s="15">
+      <c r="E64" s="2">
         <v>0</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="57"/>
-      <c r="B65" s="61"/>
-      <c r="C65" s="14" t="s">
+      <c r="A65" s="44"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="4">
         <v>25</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="57"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="14" t="s">
+      <c r="A66" s="44"/>
+      <c r="B66" s="47"/>
+      <c r="C66" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E66" s="15">
+      <c r="E66" s="2">
         <v>1000000</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="57"/>
-      <c r="B67" s="62"/>
-      <c r="C67" s="21" t="s">
+      <c r="A67" s="44"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E67" s="22">
+      <c r="E67" s="18">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="57"/>
-      <c r="B68" s="63" t="s">
+      <c r="A68" s="44"/>
+      <c r="B68" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D68" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="19">
         <v>0.997</v>
       </c>
-      <c r="F68" s="19" t="s">
+      <c r="F68" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="57"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="44"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E69" s="5">
         <v>1080</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="14" t="s">
+      <c r="A70" s="44"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E70" s="5">
         <v>12.68</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="57"/>
-      <c r="B71" s="61"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="44"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E71" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="57"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="44"/>
+      <c r="B72" s="47"/>
+      <c r="C72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="4">
         <v>25</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="44"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E73" s="33">
+      <c r="E73" s="29">
         <v>1000000</v>
       </c>
-      <c r="F73" s="14" t="s">
+      <c r="F73" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="58"/>
-      <c r="B74" s="64"/>
-      <c r="C74" s="31" t="s">
+      <c r="A74" s="45"/>
+      <c r="B74" s="50"/>
+      <c r="C74" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="31" t="s">
+      <c r="D74" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="28">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F74" s="31" t="s">
+      <c r="F74" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="56" t="s">
+      <c r="A75" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="34" t="s">
+      <c r="B75" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C75" s="35" t="s">
+      <c r="C75" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="D75" s="35" t="s">
+      <c r="D75" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E75" s="36">
+      <c r="E75" s="32">
         <v>-1E-4</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="31" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="28" t="s">
+      <c r="A76" s="44"/>
+      <c r="B76" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E76" s="17">
+      <c r="E76" s="3">
         <v>-1E-4</v>
       </c>
-      <c r="F76" s="14" t="s">
+      <c r="F76" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="57"/>
-      <c r="B77" s="37" t="s">
+      <c r="A77" s="44"/>
+      <c r="B77" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E77" s="38">
+      <c r="E77" s="34">
         <v>-1.5</v>
       </c>
-      <c r="F77" s="24" t="s">
+      <c r="F77" s="20" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="57"/>
-      <c r="B78" s="37" t="s">
+      <c r="A78" s="44"/>
+      <c r="B78" s="33" t="s">
         <v>344</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="E78" s="38">
+      <c r="E78" s="34">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="F78" s="24" t="s">
+      <c r="F78" s="20" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="58"/>
-      <c r="B79" s="26" t="s">
+      <c r="A79" s="45"/>
+      <c r="B79" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="E79" s="32">
+      <c r="E79" s="28">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
-      <c r="F79" s="31" t="s">
+      <c r="F79" s="27" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3408,43 +3386,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="14"/>
+    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -3459,425 +3437,425 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="57"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="57"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="57"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="44"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="57"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="44"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="57"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="44"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="14" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="57"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="44"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="14" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="57"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="57"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="14" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="57"/>
-      <c r="B11" s="65"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="51"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="19" t="s">
+      <c r="E12" s="16"/>
+      <c r="F12" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="57"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="14" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="1" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="57"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="14" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="14" t="s">
+      <c r="A17" s="44"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="57"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="14" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="57"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="14" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="57"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="14" t="s">
+      <c r="A20" s="44"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="14" t="s">
+      <c r="E20" s="4"/>
+      <c r="F20" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="44"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="4"/>
+      <c r="F21" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="14" t="s">
+      <c r="A22" s="44"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="14" t="s">
+      <c r="E22" s="4"/>
+      <c r="F22" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="57"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="21"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
-      <c r="B24" s="68" t="s">
+      <c r="A24" s="44"/>
+      <c r="B24" s="54" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="57"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="44"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="57"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="14" t="s">
+      <c r="A26" s="44"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="14" t="s">
+      <c r="E26" s="3"/>
+      <c r="F26" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="57"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="44"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="14" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="57"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="44"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="14" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="57"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="44"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="57"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="44"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="57"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="44"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="14" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="57"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="44"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="14" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="57"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="21"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57"/>
-      <c r="B34" s="55" t="s">
+      <c r="A34" s="44"/>
+      <c r="B34" s="42" t="s">
         <v>365</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -3892,8 +3870,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="57"/>
-      <c r="B35" s="55"/>
+      <c r="A35" s="44"/>
+      <c r="B35" s="42"/>
       <c r="C35" s="1" t="s">
         <v>107</v>
       </c>
@@ -3906,8 +3884,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="57"/>
-      <c r="B36" s="55"/>
+      <c r="A36" s="44"/>
+      <c r="B36" s="42"/>
       <c r="C36" s="1" t="s">
         <v>84</v>
       </c>
@@ -3920,8 +3898,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="57"/>
-      <c r="B37" s="55"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="42"/>
       <c r="C37" s="1" t="s">
         <v>246</v>
       </c>
@@ -3934,8 +3912,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="57"/>
-      <c r="B38" s="55"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="42"/>
       <c r="C38" s="1" t="s">
         <v>370</v>
       </c>
@@ -3948,8 +3926,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="57"/>
-      <c r="B39" s="55"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="1" t="s">
         <v>234</v>
       </c>
@@ -3962,8 +3940,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="57"/>
-      <c r="B40" s="55"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="1" t="s">
         <v>141</v>
       </c>
@@ -3976,8 +3954,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="57"/>
-      <c r="B41" s="55"/>
+      <c r="A41" s="44"/>
+      <c r="B41" s="42"/>
       <c r="C41" s="1" t="s">
         <v>155</v>
       </c>
@@ -3990,8 +3968,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="57"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="44"/>
+      <c r="B42" s="42"/>
       <c r="C42" s="1" t="s">
         <v>161</v>
       </c>
@@ -4004,8 +3982,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="57"/>
-      <c r="B43" s="55"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="1" t="s">
         <v>196</v>
       </c>
@@ -4018,8 +3996,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="57"/>
-      <c r="B44" s="55"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="42"/>
       <c r="C44" s="1" t="s">
         <v>167</v>
       </c>
@@ -4032,8 +4010,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="57"/>
-      <c r="B45" s="55"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="42"/>
       <c r="C45" s="1" t="s">
         <v>188</v>
       </c>
@@ -4046,18 +4024,15 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="57"/>
-      <c r="B46" s="55"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="42"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="56" t="s">
+      <c r="A47" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="46" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -4066,433 +4041,433 @@
       <c r="D47" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="29"/>
+      <c r="E47" s="25"/>
       <c r="F47" s="12" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="57"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="14" t="s">
+      <c r="A48" s="44"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="14" t="s">
+      <c r="E48" s="3"/>
+      <c r="F48" s="1" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="57"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="44"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="14" t="s">
+      <c r="E49" s="4"/>
+      <c r="F49" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="57"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="44"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="14" t="s">
+      <c r="E50" s="3"/>
+      <c r="F50" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="57"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="44"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="17"/>
-      <c r="F51" s="14" t="s">
+      <c r="E51" s="3"/>
+      <c r="F51" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="57"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="44"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="14" t="s">
+      <c r="E52" s="3"/>
+      <c r="F52" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="57"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="14" t="s">
+      <c r="A53" s="44"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="14" t="s">
+      <c r="E53" s="3"/>
+      <c r="F53" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="61"/>
-      <c r="C54" s="14" t="s">
+      <c r="A54" s="44"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E54" s="17"/>
-      <c r="F54" s="14" t="s">
+      <c r="E54" s="3"/>
+      <c r="F54" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="57"/>
-      <c r="B55" s="61"/>
-      <c r="C55" s="14" t="s">
+      <c r="A55" s="44"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E55" s="17"/>
-      <c r="F55" s="14" t="s">
+      <c r="E55" s="3"/>
+      <c r="F55" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="57"/>
-      <c r="B56" s="62"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="21"/>
+      <c r="A56" s="44"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="57"/>
-      <c r="B57" s="61" t="s">
+      <c r="A57" s="44"/>
+      <c r="B57" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="14" t="s">
+      <c r="E57" s="2"/>
+      <c r="F57" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="57"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="14" t="s">
+      <c r="A58" s="44"/>
+      <c r="B58" s="47"/>
+      <c r="C58" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E58" s="17"/>
-      <c r="F58" s="14" t="s">
+      <c r="E58" s="3"/>
+      <c r="F58" s="1" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="57"/>
-      <c r="B59" s="61"/>
-      <c r="C59" s="14" t="s">
+      <c r="A59" s="44"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E59" s="18"/>
-      <c r="F59" s="14" t="s">
+      <c r="E59" s="4"/>
+      <c r="F59" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="57"/>
-      <c r="B60" s="61"/>
-      <c r="C60" s="14" t="s">
+      <c r="A60" s="44"/>
+      <c r="B60" s="47"/>
+      <c r="C60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="14" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="57"/>
-      <c r="B61" s="61"/>
-      <c r="C61" s="14" t="s">
+      <c r="A61" s="44"/>
+      <c r="B61" s="47"/>
+      <c r="C61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E61" s="17"/>
-      <c r="F61" s="14" t="s">
+      <c r="E61" s="3"/>
+      <c r="F61" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="57"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="14" t="s">
+      <c r="A62" s="44"/>
+      <c r="B62" s="47"/>
+      <c r="C62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E62" s="17"/>
-      <c r="F62" s="14" t="s">
+      <c r="E62" s="3"/>
+      <c r="F62" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="57"/>
-      <c r="B63" s="61"/>
-      <c r="C63" s="14" t="s">
+      <c r="A63" s="44"/>
+      <c r="B63" s="47"/>
+      <c r="C63" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="14" t="s">
+      <c r="E63" s="3"/>
+      <c r="F63" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="57"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="14" t="s">
+      <c r="A64" s="44"/>
+      <c r="B64" s="47"/>
+      <c r="C64" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E64" s="17"/>
-      <c r="F64" s="14" t="s">
+      <c r="E64" s="3"/>
+      <c r="F64" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="57"/>
-      <c r="B65" s="61"/>
-      <c r="C65" s="14" t="s">
+      <c r="A65" s="44"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E65" s="17"/>
-      <c r="F65" s="14" t="s">
+      <c r="E65" s="3"/>
+      <c r="F65" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="57"/>
-      <c r="B66" s="62"/>
-      <c r="E66" s="17"/>
+      <c r="A66" s="44"/>
+      <c r="B66" s="48"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="57"/>
-      <c r="B67" s="63" t="s">
+      <c r="A67" s="44"/>
+      <c r="B67" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="19" t="s">
+      <c r="E67" s="19"/>
+      <c r="F67" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="57"/>
-      <c r="B68" s="61"/>
-      <c r="C68" s="14" t="s">
+      <c r="A68" s="44"/>
+      <c r="B68" s="47"/>
+      <c r="C68" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E68" s="17"/>
-      <c r="F68" s="14" t="s">
+      <c r="E68" s="3"/>
+      <c r="F68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="57"/>
-      <c r="B69" s="65"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="44"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="14" t="s">
+      <c r="E69" s="2"/>
+      <c r="F69" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="65"/>
-      <c r="C70" s="14" t="s">
+      <c r="A70" s="44"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="14" t="s">
+      <c r="E70" s="2"/>
+      <c r="F70" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="57"/>
-      <c r="B71" s="65"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="44"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="14" t="s">
+      <c r="E71" s="2"/>
+      <c r="F71" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="57"/>
-      <c r="B72" s="65"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="44"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E72" s="17"/>
-      <c r="F72" s="14" t="s">
+      <c r="E72" s="3"/>
+      <c r="F72" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="65"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="44"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="14" t="s">
+      <c r="E73" s="2"/>
+      <c r="F73" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="57"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="14" t="s">
+      <c r="A74" s="44"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E74" s="17"/>
-      <c r="F74" s="14" t="s">
+      <c r="E74" s="3"/>
+      <c r="F74" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="57"/>
-      <c r="B75" s="65"/>
-      <c r="C75" s="14" t="s">
+      <c r="A75" s="44"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E75" s="17"/>
-      <c r="F75" s="14" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="65"/>
-      <c r="C76" s="14" t="s">
+      <c r="A76" s="44"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E76" s="17"/>
-      <c r="F76" s="14" t="s">
+      <c r="E76" s="3"/>
+      <c r="F76" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="57"/>
-      <c r="B77" s="65"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="44"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E77" s="17"/>
-      <c r="F77" s="14" t="s">
+      <c r="E77" s="3"/>
+      <c r="F77" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="58"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="31"/>
+      <c r="A78" s="45"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="27"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="56" t="s">
+      <c r="A79" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="B79" s="67" t="s">
+      <c r="B79" s="53" t="s">
         <v>73</v>
       </c>
       <c r="C79" s="12" t="s">
@@ -4501,74 +4476,74 @@
       <c r="D79" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="29"/>
+      <c r="E79" s="25"/>
       <c r="F79" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="57"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="39" t="s">
+      <c r="A80" s="44"/>
+      <c r="B80" s="51"/>
+      <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="D80" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E80" s="41"/>
-      <c r="F80" s="39" t="s">
+      <c r="E80" s="2"/>
+      <c r="F80" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="57"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="21"/>
-    </row>
-    <row r="82" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="57"/>
-      <c r="B82" s="73" t="s">
+      <c r="A81" s="44"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="17"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="44"/>
+      <c r="B82" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="C82" s="49" t="s">
+      <c r="C82" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="D82" s="49" t="s">
+      <c r="D82" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="E82" s="50"/>
-      <c r="F82" s="49" t="s">
+      <c r="E82" s="16"/>
+      <c r="F82" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="57"/>
-      <c r="B83" s="74"/>
-      <c r="C83" s="51" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="44"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D83" s="51" t="s">
+      <c r="D83" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E83" s="52"/>
-      <c r="F83" s="51" t="s">
+      <c r="E83" s="2"/>
+      <c r="F83" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="57"/>
-      <c r="B84" s="75"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="54"/>
-      <c r="F84" s="53"/>
-    </row>
-    <row r="85" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="57"/>
-      <c r="B85" s="72" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="44"/>
+      <c r="B84" s="58"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="17"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="44"/>
+      <c r="B85" s="56" t="s">
         <v>380</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -4582,9 +4557,9 @@
         <v>383</v>
       </c>
     </row>
-    <row r="86" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="57"/>
-      <c r="B86" s="72"/>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="44"/>
+      <c r="B86" s="56"/>
       <c r="C86" s="1" t="s">
         <v>384</v>
       </c>
@@ -4596,280 +4571,280 @@
         <v>149</v>
       </c>
     </row>
-    <row r="87" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="57"/>
-      <c r="B87" s="72"/>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="44"/>
+      <c r="B87" s="56"/>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="57"/>
-      <c r="B88" s="63" t="s">
+      <c r="A88" s="44"/>
+      <c r="B88" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D88" s="19" t="s">
+      <c r="D88" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E88" s="23"/>
-      <c r="F88" s="19" t="s">
+      <c r="E88" s="19"/>
+      <c r="F88" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="57"/>
-      <c r="B89" s="61"/>
-      <c r="C89" s="14" t="s">
+      <c r="A89" s="44"/>
+      <c r="B89" s="47"/>
+      <c r="C89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D89" s="14" t="s">
+      <c r="D89" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" s="14" t="s">
+      <c r="F89" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="57"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="14" t="s">
+      <c r="A90" s="44"/>
+      <c r="B90" s="47"/>
+      <c r="C90" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E90" s="5"/>
-      <c r="F90" s="14" t="s">
+      <c r="F90" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="57"/>
-      <c r="B91" s="61"/>
-      <c r="C91" s="14" t="s">
+      <c r="A91" s="44"/>
+      <c r="B91" s="47"/>
+      <c r="C91" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D91" s="14" t="s">
+      <c r="D91" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="14" t="s">
+      <c r="E91" s="2"/>
+      <c r="F91" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="57"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="14" t="s">
+      <c r="A92" s="44"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="14" t="s">
+      <c r="E92" s="4"/>
+      <c r="F92" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="57"/>
-      <c r="B93" s="61"/>
-      <c r="C93" s="14" t="s">
+      <c r="A93" s="44"/>
+      <c r="B93" s="47"/>
+      <c r="C93" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E93" s="15"/>
-      <c r="F93" s="14" t="s">
+      <c r="E93" s="2"/>
+      <c r="F93" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="57"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="14" t="s">
+      <c r="A94" s="44"/>
+      <c r="B94" s="47"/>
+      <c r="C94" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E94" s="15"/>
-      <c r="F94" s="14" t="s">
+      <c r="E94" s="2"/>
+      <c r="F94" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="57"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="14" t="s">
+      <c r="A95" s="44"/>
+      <c r="B95" s="47"/>
+      <c r="C95" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D95" s="14" t="s">
+      <c r="D95" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E95" s="17"/>
-      <c r="F95" s="14" t="s">
+      <c r="E95" s="3"/>
+      <c r="F95" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="57"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="14" t="s">
+      <c r="A96" s="44"/>
+      <c r="B96" s="47"/>
+      <c r="C96" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E96" s="17"/>
-      <c r="F96" s="14" t="s">
+      <c r="E96" s="3"/>
+      <c r="F96" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="57"/>
-      <c r="B97" s="62"/>
+      <c r="A97" s="44"/>
+      <c r="B97" s="48"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="57"/>
-      <c r="B98" s="63" t="s">
+      <c r="A98" s="44"/>
+      <c r="B98" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="19" t="s">
+      <c r="C98" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D98" s="19" t="s">
+      <c r="D98" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E98" s="23"/>
-      <c r="F98" s="19" t="s">
+      <c r="E98" s="19"/>
+      <c r="F98" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="57"/>
-      <c r="B99" s="61"/>
-      <c r="C99" s="14" t="s">
+      <c r="A99" s="44"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D99" s="14" t="s">
+      <c r="D99" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E99" s="5"/>
-      <c r="F99" s="14" t="s">
+      <c r="F99" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="57"/>
-      <c r="B100" s="61"/>
-      <c r="C100" s="14" t="s">
+      <c r="A100" s="44"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D100" s="14" t="s">
+      <c r="D100" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E100" s="5"/>
-      <c r="F100" s="14" t="s">
+      <c r="F100" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="57"/>
-      <c r="B101" s="61"/>
-      <c r="C101" s="14" t="s">
+      <c r="A101" s="44"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D101" s="14" t="s">
+      <c r="D101" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E101" s="5"/>
-      <c r="F101" s="14" t="s">
+      <c r="F101" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="57"/>
-      <c r="B102" s="61"/>
-      <c r="C102" s="14" t="s">
+      <c r="A102" s="44"/>
+      <c r="B102" s="47"/>
+      <c r="C102" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D102" s="14" t="s">
+      <c r="D102" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E102" s="18"/>
-      <c r="F102" s="14" t="s">
+      <c r="E102" s="4"/>
+      <c r="F102" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="57"/>
-      <c r="B103" s="61"/>
-      <c r="C103" s="14" t="s">
+      <c r="A103" s="44"/>
+      <c r="B103" s="47"/>
+      <c r="C103" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D103" s="14" t="s">
+      <c r="D103" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E103" s="33"/>
-      <c r="F103" s="14" t="s">
+      <c r="E103" s="29"/>
+      <c r="F103" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="57"/>
-      <c r="B104" s="61"/>
-      <c r="C104" s="14" t="s">
+      <c r="A104" s="44"/>
+      <c r="B104" s="47"/>
+      <c r="C104" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E104" s="33"/>
-      <c r="F104" s="14" t="s">
+      <c r="E104" s="29"/>
+      <c r="F104" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="57"/>
-      <c r="B105" s="61"/>
-      <c r="C105" s="14" t="s">
+      <c r="A105" s="44"/>
+      <c r="B105" s="47"/>
+      <c r="C105" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D105" s="14" t="s">
+      <c r="D105" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E105" s="17"/>
-      <c r="F105" s="14" t="s">
+      <c r="E105" s="3"/>
+      <c r="F105" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="57"/>
-      <c r="B106" s="61"/>
-      <c r="C106" s="14" t="s">
+      <c r="A106" s="44"/>
+      <c r="B106" s="47"/>
+      <c r="C106" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D106" s="14" t="s">
+      <c r="D106" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E106" s="17"/>
-      <c r="F106" s="14" t="s">
+      <c r="E106" s="3"/>
+      <c r="F106" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="58"/>
-      <c r="B107" s="64"/>
+      <c r="A107" s="45"/>
+      <c r="B107" s="50"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="56" t="s">
+      <c r="A108" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="B108" s="67" t="s">
+      <c r="B108" s="53" t="s">
         <v>73</v>
       </c>
       <c r="C108" s="12" t="s">
@@ -4884,209 +4859,209 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="57"/>
-      <c r="B109" s="65"/>
-      <c r="C109" s="14" t="s">
+      <c r="A109" s="44"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D109" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E109" s="17"/>
-      <c r="F109" s="14" t="s">
+      <c r="E109" s="3"/>
+      <c r="F109" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="57"/>
-      <c r="B110" s="65"/>
-      <c r="C110" s="14" t="s">
+      <c r="A110" s="44"/>
+      <c r="B110" s="51"/>
+      <c r="C110" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="D110" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E110" s="17"/>
-      <c r="F110" s="14" t="s">
+      <c r="E110" s="3"/>
+      <c r="F110" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="57"/>
-      <c r="B111" s="69"/>
-      <c r="C111" s="21"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="21"/>
+      <c r="A111" s="44"/>
+      <c r="B111" s="55"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="17"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="17"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="57"/>
-      <c r="B112" s="68" t="s">
+      <c r="A112" s="44"/>
+      <c r="B112" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D112" s="14" t="s">
+      <c r="D112" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E112" s="17"/>
-      <c r="F112" s="14" t="s">
+      <c r="E112" s="3"/>
+      <c r="F112" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="57"/>
-      <c r="B113" s="65"/>
-      <c r="C113" s="14" t="s">
+      <c r="A113" s="44"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D113" s="14" t="s">
+      <c r="D113" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E113" s="17"/>
-      <c r="F113" s="14" t="s">
+      <c r="E113" s="3"/>
+      <c r="F113" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="57"/>
-      <c r="B114" s="65"/>
-      <c r="C114" s="14" t="s">
+      <c r="A114" s="44"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D114" s="14" t="s">
+      <c r="D114" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E114" s="17"/>
-      <c r="F114" s="14" t="s">
+      <c r="E114" s="3"/>
+      <c r="F114" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="57"/>
-      <c r="B115" s="69"/>
-      <c r="E115" s="17"/>
+      <c r="A115" s="44"/>
+      <c r="B115" s="55"/>
+      <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="57"/>
-      <c r="B116" s="68" t="s">
+      <c r="A116" s="44"/>
+      <c r="B116" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E116" s="23"/>
-      <c r="F116" s="19" t="s">
+      <c r="E116" s="19"/>
+      <c r="F116" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="57"/>
-      <c r="B117" s="70"/>
-      <c r="C117" s="39" t="s">
+      <c r="A117" s="44"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D117" s="39" t="s">
+      <c r="D117" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E117" s="40"/>
-      <c r="F117" s="39" t="s">
+      <c r="E117" s="3"/>
+      <c r="F117" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="57"/>
-      <c r="B118" s="69"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="22"/>
-      <c r="F118" s="21"/>
+      <c r="A118" s="44"/>
+      <c r="B118" s="55"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="17"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="17"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="57"/>
-      <c r="B119" s="68" t="s">
+      <c r="A119" s="44"/>
+      <c r="B119" s="54" t="s">
         <v>344</v>
       </c>
-      <c r="C119" s="19" t="s">
+      <c r="C119" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="D119" s="19" t="s">
+      <c r="D119" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="E119" s="23"/>
-      <c r="F119" s="19" t="s">
+      <c r="E119" s="19"/>
+      <c r="F119" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="57"/>
-      <c r="B120" s="70"/>
-      <c r="C120" s="39" t="s">
+      <c r="A120" s="44"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D120" s="39" t="s">
+      <c r="D120" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E120" s="40"/>
-      <c r="F120" s="39" t="s">
+      <c r="E120" s="3"/>
+      <c r="F120" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="57"/>
-      <c r="B121" s="69"/>
-      <c r="C121" s="21"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="21"/>
+      <c r="A121" s="44"/>
+      <c r="B121" s="55"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="17"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="57"/>
-      <c r="B122" s="70" t="s">
+      <c r="A122" s="44"/>
+      <c r="B122" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D122" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E122" s="17"/>
-      <c r="F122" s="14" t="s">
+      <c r="E122" s="3"/>
+      <c r="F122" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="57"/>
-      <c r="B123" s="65"/>
-      <c r="C123" s="14" t="s">
+      <c r="A123" s="44"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D123" s="14" t="s">
+      <c r="D123" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E123" s="17"/>
-      <c r="F123" s="14" t="s">
+      <c r="E123" s="3"/>
+      <c r="F123" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="58"/>
-      <c r="B124" s="66"/>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="32"/>
-      <c r="F124" s="31"/>
+      <c r="A124" s="45"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="27"/>
+      <c r="D124" s="27"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="27"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="56" t="s">
+      <c r="A125" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="B125" s="67" t="s">
+      <c r="B125" s="53" t="s">
         <v>13</v>
       </c>
       <c r="C125" s="12" t="s">
@@ -5101,426 +5076,411 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="59"/>
-      <c r="B126" s="70"/>
-      <c r="C126" s="14" t="s">
+      <c r="A126" s="44"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D126" s="14" t="s">
+      <c r="D126" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F126" s="14" t="s">
+      <c r="F126" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="59"/>
-      <c r="B127" s="69"/>
-      <c r="C127" s="21"/>
-      <c r="D127" s="21"/>
-      <c r="E127" s="21"/>
-      <c r="F127" s="21"/>
+      <c r="A127" s="44"/>
+      <c r="B127" s="55"/>
+      <c r="C127" s="17"/>
+      <c r="D127" s="17"/>
+      <c r="E127" s="17"/>
+      <c r="F127" s="17"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="59"/>
-      <c r="B128" s="68" t="s">
+      <c r="A128" s="44"/>
+      <c r="B128" s="54" t="s">
         <v>183</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D128" s="14" t="s">
+      <c r="D128" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F128" s="14" t="s">
+      <c r="F128" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="59"/>
-      <c r="B129" s="70"/>
-      <c r="C129" s="14" t="s">
+      <c r="A129" s="44"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D129" s="14" t="s">
+      <c r="D129" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F129" s="14" t="s">
+      <c r="F129" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="59"/>
-      <c r="B130" s="70"/>
-      <c r="C130" s="14" t="s">
+      <c r="A130" s="44"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="14" t="s">
+      <c r="D130" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F130" s="14" t="s">
+      <c r="F130" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="59"/>
-      <c r="B131" s="70"/>
-      <c r="C131" s="14" t="s">
+      <c r="A131" s="44"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D131" s="14" t="s">
+      <c r="D131" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F131" s="14" t="s">
+      <c r="F131" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="59"/>
-      <c r="B132" s="70"/>
-      <c r="C132" s="14" t="s">
+      <c r="A132" s="44"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D132" s="14" t="s">
+      <c r="D132" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F132" s="14" t="s">
+      <c r="F132" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="59"/>
-      <c r="B133" s="70"/>
-      <c r="C133" s="14" t="s">
+      <c r="A133" s="44"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D133" s="14" t="s">
+      <c r="D133" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F133" s="14" t="s">
+      <c r="F133" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="59"/>
-      <c r="B134" s="69"/>
+      <c r="A134" s="44"/>
+      <c r="B134" s="55"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="59"/>
-      <c r="B135" s="68" t="s">
+      <c r="A135" s="44"/>
+      <c r="B135" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="D135" s="19" t="s">
+      <c r="D135" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="E135" s="19"/>
-      <c r="F135" s="19" t="s">
+      <c r="E135" s="15"/>
+      <c r="F135" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="59"/>
-      <c r="B136" s="70"/>
-      <c r="C136" s="14" t="s">
+      <c r="A136" s="44"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D136" s="14" t="s">
+      <c r="D136" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F136" s="14" t="s">
+      <c r="F136" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="59"/>
-      <c r="B137" s="70"/>
-      <c r="C137" s="14" t="s">
+      <c r="A137" s="44"/>
+      <c r="B137" s="51"/>
+      <c r="C137" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D137" s="14" t="s">
+      <c r="D137" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F137" s="14" t="s">
+      <c r="F137" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="59"/>
-      <c r="B138" s="70"/>
-      <c r="C138" s="14" t="s">
+      <c r="A138" s="44"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D138" s="14" t="s">
+      <c r="D138" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F138" s="14" t="s">
+      <c r="F138" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="59"/>
-      <c r="B139" s="70"/>
-      <c r="C139" s="14" t="s">
+      <c r="A139" s="44"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D139" s="14" t="s">
+      <c r="D139" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F139" s="14" t="s">
+      <c r="F139" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="59"/>
-      <c r="B140" s="70"/>
-      <c r="C140" s="14" t="s">
+      <c r="A140" s="44"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D140" s="14" t="s">
+      <c r="D140" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F140" s="14" t="s">
+      <c r="F140" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="59"/>
-      <c r="B141" s="70"/>
-      <c r="C141" s="14" t="s">
+      <c r="A141" s="44"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D141" s="14" t="s">
+      <c r="D141" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F141" s="14" t="s">
+      <c r="F141" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="59"/>
-      <c r="B142" s="70"/>
-      <c r="C142" s="14" t="s">
+      <c r="A142" s="44"/>
+      <c r="B142" s="51"/>
+      <c r="C142" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D142" s="14" t="s">
+      <c r="D142" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F142" s="14" t="s">
+      <c r="F142" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="59"/>
-      <c r="B143" s="70"/>
-      <c r="C143" s="14" t="s">
+      <c r="A143" s="44"/>
+      <c r="B143" s="51"/>
+      <c r="C143" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D143" s="14" t="s">
+      <c r="D143" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F143" s="14" t="s">
+      <c r="F143" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="59"/>
-      <c r="B144" s="70"/>
-      <c r="C144" s="14" t="s">
+      <c r="A144" s="44"/>
+      <c r="B144" s="51"/>
+      <c r="C144" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D144" s="14" t="s">
+      <c r="D144" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F144" s="14" t="s">
+      <c r="F144" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="59"/>
-      <c r="B145" s="70"/>
-      <c r="C145" s="14" t="s">
+      <c r="A145" s="44"/>
+      <c r="B145" s="51"/>
+      <c r="C145" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D145" s="14" t="s">
+      <c r="D145" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F145" s="14" t="s">
+      <c r="F145" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="59"/>
-      <c r="B146" s="70"/>
-      <c r="C146" s="14" t="s">
+      <c r="A146" s="44"/>
+      <c r="B146" s="51"/>
+      <c r="C146" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D146" s="14" t="s">
+      <c r="D146" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F146" s="14" t="s">
+      <c r="F146" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="59"/>
-      <c r="B147" s="70"/>
-      <c r="C147" s="14" t="s">
+      <c r="A147" s="44"/>
+      <c r="B147" s="51"/>
+      <c r="C147" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D147" s="14" t="s">
+      <c r="D147" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F147" s="14" t="s">
+      <c r="F147" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="59"/>
-      <c r="B148" s="70"/>
-      <c r="C148" s="14" t="s">
+      <c r="A148" s="44"/>
+      <c r="B148" s="51"/>
+      <c r="C148" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D148" s="14" t="s">
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F148" s="14" t="s">
+      <c r="F148" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="59"/>
-      <c r="B149" s="69"/>
+      <c r="A149" s="44"/>
+      <c r="B149" s="55"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="59"/>
-      <c r="B150" s="68" t="s">
+      <c r="A150" s="44"/>
+      <c r="B150" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="C150" s="19" t="s">
+      <c r="C150" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="D150" s="19" t="s">
+      <c r="D150" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E150" s="19"/>
-      <c r="F150" s="19" t="s">
+      <c r="E150" s="15"/>
+      <c r="F150" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="59"/>
-      <c r="B151" s="70"/>
-      <c r="C151" s="39" t="s">
+      <c r="A151" s="44"/>
+      <c r="B151" s="51"/>
+      <c r="C151" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D151" s="39" t="s">
+      <c r="D151" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E151" s="39"/>
-      <c r="F151" s="39" t="s">
+      <c r="F151" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="59"/>
-      <c r="B152" s="70"/>
-      <c r="C152" s="39" t="s">
+      <c r="A152" s="44"/>
+      <c r="B152" s="51"/>
+      <c r="C152" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D152" s="39" t="s">
+      <c r="D152" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E152" s="39"/>
-      <c r="F152" s="39" t="s">
+      <c r="F152" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="59"/>
-      <c r="B153" s="70"/>
-      <c r="C153" s="39" t="s">
+      <c r="A153" s="44"/>
+      <c r="B153" s="51"/>
+      <c r="C153" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D153" s="39" t="s">
+      <c r="D153" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E153" s="39"/>
-      <c r="F153" s="39" t="s">
+      <c r="F153" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="59"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="39" t="s">
+      <c r="A154" s="44"/>
+      <c r="B154" s="51"/>
+      <c r="C154" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D154" s="39" t="s">
+      <c r="D154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E154" s="39"/>
-      <c r="F154" s="39" t="s">
+      <c r="F154" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="59"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="21"/>
-      <c r="D155" s="21"/>
-      <c r="E155" s="21"/>
-      <c r="F155" s="21"/>
+      <c r="A155" s="44"/>
+      <c r="B155" s="55"/>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="17"/>
+      <c r="F155" s="17"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="59"/>
-      <c r="B156" s="71" t="s">
+      <c r="A156" s="44"/>
+      <c r="B156" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="C156" s="39" t="s">
+      <c r="C156" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D156" s="39" t="s">
+      <c r="D156" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E156" s="39"/>
-      <c r="F156" s="39" t="s">
+      <c r="F156" s="1" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="59"/>
-      <c r="B157" s="71"/>
-      <c r="C157" s="39" t="s">
+      <c r="A157" s="44"/>
+      <c r="B157" s="59"/>
+      <c r="C157" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D157" s="39" t="s">
+      <c r="D157" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E157" s="39"/>
-      <c r="F157" s="39" t="s">
+      <c r="F157" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C158" s="39"/>
-      <c r="D158" s="39"/>
-      <c r="E158" s="39"/>
-      <c r="F158" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="A47:A78"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B47:B56"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B150:B155"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A125:A157"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B135:B149"/>
+    <mergeCell ref="B128:B134"/>
     <mergeCell ref="B122:B124"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="A79:A107"/>
@@ -5533,12 +5493,15 @@
     <mergeCell ref="B119:B121"/>
     <mergeCell ref="B85:B87"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B150:B155"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A125:A157"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B135:B149"/>
-    <mergeCell ref="B128:B134"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="A47:A78"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B47:B56"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="B34:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Fischer_Tropsch/FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_H2_Brownfield_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9D341D-92D8-4EB3-A1D1-BA2B8370CD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE1DB43-2B55-442F-90B2-142713447C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-2400" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="411">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -857,12 +857,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>kWh/kg_CO2</t>
   </si>
   <si>
@@ -980,13 +974,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1426,10 +1414,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1589,46 +1577,46 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1641,7 +1629,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1684,6 +1672,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1692,9 +1683,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2173,19 +2161,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="44"/>
       <c r="B8" s="54" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E8" s="16">
         <v>38.99</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2195,7 +2183,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E9" s="2">
         <v>285.39999999999998</v>
@@ -2211,13 +2199,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E10" s="2">
         <v>2440</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2227,7 +2215,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E11" s="3">
         <v>0.03</v>
@@ -2243,45 +2231,45 @@
         <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E12" s="2">
         <v>0.63</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="44"/>
       <c r="B13" s="51"/>
       <c r="C13" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E13" s="2">
         <v>4.8600000000000003</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="44"/>
       <c r="B14" s="51"/>
       <c r="C14" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E14" s="2">
         <v>0.39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2291,7 +2279,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E15" s="4">
         <v>20</v>
@@ -2307,7 +2295,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E16" s="18">
         <v>7.0000000000000007E-2</v>
@@ -2319,13 +2307,13 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="44"/>
       <c r="B17" s="54" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E17" s="19">
         <v>3.7</v>
@@ -2341,13 +2329,13 @@
         <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="3">
         <v>0.27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2357,13 +2345,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E19" s="3">
         <v>700</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2373,7 +2361,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" s="3">
         <v>0.02</v>
@@ -2389,7 +2377,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E21" s="3">
         <v>20</v>
@@ -2405,7 +2393,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E22" s="18">
         <v>0.05</v>
@@ -2417,35 +2405,35 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="42" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E23" s="11">
         <v>0.2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="44"/>
       <c r="B24" s="42"/>
       <c r="C24" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E24" s="11">
         <v>0.92800000000000005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2455,23 +2443,23 @@
         <v>10</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E25" s="11">
         <v>1640</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="44"/>
       <c r="B26" s="42"/>
       <c r="C26" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E26" s="10">
         <v>0.04</v>
@@ -2484,48 +2472,48 @@
       <c r="A27" s="44"/>
       <c r="B27" s="42"/>
       <c r="C27" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E27" s="10">
         <v>2.5</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="44"/>
       <c r="B28" s="42"/>
       <c r="C28" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E28" s="7">
         <v>1.5</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="44"/>
       <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E29" s="7">
         <v>1.5E-3</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2535,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E30" s="9">
         <v>25</v>
@@ -2551,7 +2539,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E31" s="10">
         <v>0.08</v>
@@ -2695,19 +2683,19 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="44"/>
       <c r="B40" s="49" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>87</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E40" s="25">
         <v>2.83</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2717,7 +2705,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E41" s="3">
         <v>0.03</v>
@@ -2733,7 +2721,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E42" s="4">
         <v>30</v>
@@ -2749,7 +2737,7 @@
         <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E43" s="3">
         <v>7.3999999999999999E-4</v>
@@ -2765,7 +2753,7 @@
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E44" s="3">
         <v>0.98</v>
@@ -2781,7 +2769,7 @@
         <v>36</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E45" s="3">
         <v>0.98</v>
@@ -2797,7 +2785,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E46" s="3">
         <v>0.05</v>
@@ -2813,7 +2801,7 @@
         <v>88</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E47" s="18">
         <v>0</v>
@@ -3008,13 +2996,13 @@
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="44"/>
       <c r="B59" s="39" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E59" s="41">
         <v>5</v>
@@ -3026,13 +3014,13 @@
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="44"/>
       <c r="B60" s="36" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E60" s="10">
         <v>0</v>
@@ -3283,7 +3271,7 @@
         <v>78</v>
       </c>
       <c r="E75" s="32">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="31" t="s">
         <v>19</v>
@@ -3292,19 +3280,19 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="44"/>
       <c r="B76" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E76" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3328,38 +3316,38 @@
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="44"/>
       <c r="B78" s="33" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E78" s="34">
         <v>-0.55000000000000004</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="45"/>
       <c r="B79" s="22" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E79" s="28">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3386,7 +3374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
@@ -3556,13 +3544,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="44"/>
       <c r="B12" s="54" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15" t="s">
@@ -3573,28 +3561,28 @@
       <c r="A13" s="44"/>
       <c r="B13" s="51"/>
       <c r="C13" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="44"/>
       <c r="B14" s="51"/>
       <c r="C14" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3604,7 +3592,7 @@
         <v>139</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
@@ -3615,14 +3603,14 @@
       <c r="A16" s="44"/>
       <c r="B16" s="51"/>
       <c r="C16" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3632,7 +3620,7 @@
         <v>84</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="1" t="s">
@@ -3646,7 +3634,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="1" t="s">
@@ -3660,7 +3648,7 @@
         <v>155</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="1" t="s">
@@ -3674,7 +3662,7 @@
         <v>196</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="1" t="s">
@@ -3688,7 +3676,7 @@
         <v>167</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="1" t="s">
@@ -3702,7 +3690,7 @@
         <v>188</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="1" t="s">
@@ -3720,17 +3708,17 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="44"/>
       <c r="B24" s="54" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -3740,7 +3728,7 @@
         <v>107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="1" t="s">
@@ -3754,25 +3742,25 @@
         <v>84</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="44"/>
       <c r="B27" s="51"/>
       <c r="C27" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,7 +3770,7 @@
         <v>141</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="1" t="s">
@@ -3796,7 +3784,7 @@
         <v>155</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="1" t="s">
@@ -3810,7 +3798,7 @@
         <v>196</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
@@ -3824,7 +3812,7 @@
         <v>167</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="1" t="s">
@@ -3838,7 +3826,7 @@
         <v>188</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="1" t="s">
@@ -3856,13 +3844,13 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="42" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="1" t="s">
@@ -3876,7 +3864,7 @@
         <v>107</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="1" t="s">
@@ -3890,7 +3878,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
@@ -3901,42 +3889,42 @@
       <c r="A37" s="44"/>
       <c r="B37" s="42"/>
       <c r="C37" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="44"/>
       <c r="B38" s="42"/>
       <c r="C38" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="44"/>
       <c r="B39" s="42"/>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -3946,7 +3934,7 @@
         <v>141</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="1" t="s">
@@ -3960,7 +3948,7 @@
         <v>155</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="1" t="s">
@@ -3974,7 +3962,7 @@
         <v>161</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="1" t="s">
@@ -3988,7 +3976,7 @@
         <v>196</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="1" t="s">
@@ -4002,7 +3990,7 @@
         <v>167</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="1" t="s">
@@ -4016,7 +4004,7 @@
         <v>188</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="1" t="s">
@@ -4043,7 +4031,7 @@
       </c>
       <c r="E47" s="25"/>
       <c r="F47" s="12" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -4057,7 +4045,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -4169,17 +4157,17 @@
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="44"/>
       <c r="B57" s="47" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4189,11 +4177,11 @@
         <v>111</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4203,11 +4191,11 @@
         <v>135</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4217,11 +4205,11 @@
         <v>136</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4231,7 +4219,7 @@
         <v>141</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="1" t="s">
@@ -4245,7 +4233,7 @@
         <v>155</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="1" t="s">
@@ -4259,7 +4247,7 @@
         <v>196</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="1" t="s">
@@ -4273,7 +4261,7 @@
         <v>167</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="1" t="s">
@@ -4287,7 +4275,7 @@
         <v>188</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="1" t="s">
@@ -4505,14 +4493,14 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="44"/>
-      <c r="B82" s="57" t="s">
-        <v>408</v>
+      <c r="B82" s="58" t="s">
+        <v>404</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E82" s="16"/>
       <c r="F82" s="15" t="s">
@@ -4521,12 +4509,12 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="44"/>
-      <c r="B83" s="56"/>
+      <c r="B83" s="57"/>
       <c r="C83" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
@@ -4535,7 +4523,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="44"/>
-      <c r="B84" s="58"/>
+      <c r="B84" s="59"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
       <c r="E84" s="38"/>
@@ -4543,28 +4531,28 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="44"/>
-      <c r="B85" s="56" t="s">
-        <v>380</v>
+      <c r="B85" s="57" t="s">
+        <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="44"/>
-      <c r="B86" s="56"/>
+      <c r="B86" s="57"/>
       <c r="C86" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="1" t="s">
@@ -4573,7 +4561,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="44"/>
-      <c r="B87" s="56"/>
+      <c r="B87" s="57"/>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,10 +4850,10 @@
       <c r="A109" s="44"/>
       <c r="B109" s="51"/>
       <c r="C109" s="1" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="1" t="s">
@@ -4874,238 +4862,236 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="44"/>
-      <c r="B110" s="51"/>
-      <c r="C110" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E110" s="3"/>
-      <c r="F110" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B110" s="55"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="17"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="17"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="44"/>
-      <c r="B111" s="55"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="17"/>
+      <c r="B111" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="44"/>
-      <c r="B112" s="54" t="s">
-        <v>265</v>
-      </c>
+      <c r="B112" s="51"/>
       <c r="C112" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="1" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="44"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>268</v>
-      </c>
+      <c r="B113" s="55"/>
       <c r="E113" s="3"/>
-      <c r="F113" s="1" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="44"/>
-      <c r="B114" s="51"/>
-      <c r="C114" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E114" s="3"/>
-      <c r="F114" s="1" t="s">
-        <v>149</v>
+      <c r="B114" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E114" s="19"/>
+      <c r="F114" s="15" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="44"/>
-      <c r="B115" s="55"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E115" s="3"/>
+      <c r="F115" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="44"/>
-      <c r="B116" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="C116" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D116" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E116" s="19"/>
-      <c r="F116" s="15" t="s">
-        <v>132</v>
-      </c>
+      <c r="B116" s="55"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="17"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="44"/>
-      <c r="B117" s="51"/>
-      <c r="C117" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E117" s="3"/>
-      <c r="F117" s="1" t="s">
-        <v>149</v>
+      <c r="B117" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="E117" s="19"/>
+      <c r="F117" s="15" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="44"/>
-      <c r="B118" s="55"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="17"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="17"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="44"/>
-      <c r="B119" s="54" t="s">
-        <v>344</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="E119" s="19"/>
-      <c r="F119" s="15" t="s">
-        <v>350</v>
-      </c>
+      <c r="B119" s="55"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="17"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="44"/>
-      <c r="B120" s="51"/>
+      <c r="B120" s="51" t="s">
+        <v>300</v>
+      </c>
       <c r="C120" s="1" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="1" t="s">
-        <v>149</v>
+        <v>327</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="44"/>
-      <c r="B121" s="55"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="18"/>
-      <c r="F121" s="17"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="44"/>
-      <c r="B122" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E122" s="3"/>
-      <c r="F122" s="1" t="s">
+      <c r="B121" s="51"/>
+      <c r="C121" s="1" t="s">
         <v>331</v>
       </c>
+      <c r="D121" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="45"/>
+      <c r="B122" s="52"/>
+      <c r="C122" s="27"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="27"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="44"/>
-      <c r="B123" s="51"/>
-      <c r="C123" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E123" s="3"/>
-      <c r="F123" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="45"/>
-      <c r="B124" s="52"/>
-      <c r="C124" s="27"/>
-      <c r="D124" s="27"/>
-      <c r="E124" s="28"/>
-      <c r="F124" s="27"/>
+      <c r="A123" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="B123" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="44"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="B125" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E125" s="12"/>
-      <c r="F125" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="A125" s="44"/>
+      <c r="B125" s="55"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="17"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="44"/>
-      <c r="B126" s="51"/>
+      <c r="B126" s="54" t="s">
+        <v>183</v>
+      </c>
       <c r="C126" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="44"/>
-      <c r="B127" s="55"/>
-      <c r="C127" s="17"/>
-      <c r="D127" s="17"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="17"/>
+      <c r="B127" s="51"/>
+      <c r="C127" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="44"/>
-      <c r="B128" s="54" t="s">
-        <v>183</v>
-      </c>
+      <c r="B128" s="51"/>
       <c r="C128" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>149</v>
@@ -5115,10 +5101,10 @@
       <c r="A129" s="44"/>
       <c r="B129" s="51"/>
       <c r="C129" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>272</v>
+        <v>178</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>149</v>
@@ -5128,10 +5114,10 @@
       <c r="A130" s="44"/>
       <c r="B130" s="51"/>
       <c r="C130" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>149</v>
@@ -5141,10 +5127,10 @@
       <c r="A131" s="44"/>
       <c r="B131" s="51"/>
       <c r="C131" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>149</v>
@@ -5152,58 +5138,58 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="44"/>
-      <c r="B132" s="51"/>
-      <c r="C132" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B132" s="55"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="44"/>
-      <c r="B133" s="51"/>
-      <c r="C133" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>149</v>
+      <c r="B133" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E133" s="15"/>
+      <c r="F133" s="15" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="44"/>
-      <c r="B134" s="55"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="44"/>
-      <c r="B135" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="E135" s="15"/>
-      <c r="F135" s="15" t="s">
-        <v>208</v>
+      <c r="B135" s="51"/>
+      <c r="C135" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="44"/>
       <c r="B136" s="51"/>
       <c r="C136" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>208</v>
@@ -5213,88 +5199,88 @@
       <c r="A137" s="44"/>
       <c r="B137" s="51"/>
       <c r="C137" s="1" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="44"/>
       <c r="B138" s="51"/>
       <c r="C138" s="1" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>208</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="44"/>
       <c r="B139" s="51"/>
       <c r="C139" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="44"/>
       <c r="B140" s="51"/>
       <c r="C140" s="1" t="s">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="44"/>
       <c r="B141" s="51"/>
       <c r="C141" s="1" t="s">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>277</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="44"/>
       <c r="B142" s="51"/>
       <c r="C142" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="44"/>
       <c r="B143" s="51"/>
       <c r="C143" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>211</v>
+        <v>400</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>212</v>
@@ -5304,36 +5290,36 @@
       <c r="A144" s="44"/>
       <c r="B144" s="51"/>
       <c r="C144" s="1" t="s">
-        <v>202</v>
+        <v>352</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>220</v>
+        <v>351</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="44"/>
       <c r="B145" s="51"/>
       <c r="C145" s="1" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="44"/>
       <c r="B146" s="51"/>
       <c r="C146" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>213</v>
@@ -5341,158 +5327,114 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="44"/>
-      <c r="B147" s="51"/>
-      <c r="C147" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="B147" s="55"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="44"/>
-      <c r="B148" s="51"/>
-      <c r="C148" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>213</v>
+      <c r="B148" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C148" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E148" s="15"/>
+      <c r="F148" s="15" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="44"/>
-      <c r="B149" s="55"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="44"/>
-      <c r="B150" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="C150" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E150" s="15"/>
-      <c r="F150" s="15" t="s">
-        <v>208</v>
+      <c r="B150" s="51"/>
+      <c r="C150" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="44"/>
       <c r="B151" s="51"/>
       <c r="C151" s="1" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>277</v>
+        <v>212</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="44"/>
       <c r="B152" s="51"/>
       <c r="C152" s="1" t="s">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>226</v>
+        <v>336</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="44"/>
-      <c r="B153" s="51"/>
-      <c r="C153" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>212</v>
-      </c>
+      <c r="B153" s="55"/>
+      <c r="C153" s="17"/>
+      <c r="D153" s="17"/>
+      <c r="E153" s="17"/>
+      <c r="F153" s="17"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="44"/>
-      <c r="B154" s="51"/>
+      <c r="B154" s="56" t="s">
+        <v>355</v>
+      </c>
       <c r="C154" s="1" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>213</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="44"/>
-      <c r="B155" s="55"/>
-      <c r="C155" s="17"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="17"/>
-      <c r="F155" s="17"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="44"/>
-      <c r="B156" s="59" t="s">
+      <c r="B155" s="56"/>
+      <c r="C155" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="44"/>
-      <c r="B157" s="59"/>
-      <c r="C157" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>318</v>
+      <c r="F155" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B150:B155"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A125:A157"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B135:B149"/>
-    <mergeCell ref="B128:B134"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="A79:A107"/>
-    <mergeCell ref="B88:B97"/>
-    <mergeCell ref="B98:B107"/>
-    <mergeCell ref="A108:A124"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B82:B84"/>
     <mergeCell ref="A2:A46"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B23"/>
@@ -5502,6 +5444,24 @@
     <mergeCell ref="B47:B56"/>
     <mergeCell ref="B57:B66"/>
     <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="A79:A107"/>
+    <mergeCell ref="B88:B97"/>
+    <mergeCell ref="B98:B107"/>
+    <mergeCell ref="A108:A122"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A123:A155"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="B133:B147"/>
+    <mergeCell ref="B126:B132"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
